--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_02_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_02_22_Cau.xlsx
@@ -673,7 +673,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mục tiêu là trả truy vấn đúng, không tối thiểu hóa số lượng chunk.</t>
+          <t>Số lượng chunk ít không đồng nghĩa với chất lượng truy xuất cao. Nếu một chiến lược chia chunk bỏ sót toàn bộ các truy vấn về ngoại lệ, cần thay đổi hoặc kết hợp chiến lược chia chunk (ví dụ phân cấp hoặc theo ranh giới cấu trúc) để đảm bảo độ bao phủ bằng chứng.</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Pooling chỉ xảy ra sau khi đã có token representations.</t>
+          <t>Quy trình kỹ thuật chuẩn để tạo vector embedding từ một đoạn văn bản: 1. Tokenize văn bản đầu vào (o2) -&gt; 2. Encoder tạo biểu diễn ngữ cảnh cho các token (o4) -&gt; 3. Áp dụng pooling (mean/CLS) để tổng hợp các token representations thành một vector (o1) -&gt; 4. Xuất ra và chuẩn hóa vector cuối cùng (o3).</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>0.447</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
@@ -963,7 +967,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là tích hai độ lớn.</t>
+          <t>Độ tương đồng cosine: cos(θ) = (a · b) / (||a|| × ||b||). Với a = [1, 2] và b = [2, 0]: a · b = 1×2 + 2×0 = 2; ||a|| = √(1² + 2²) = √5 ≈ 2,23607; ||b|| = √(2² + 0²) = 2. Do đó cos(θ) = 2 / (√5 × 2) = 1 / √5 ≈ 0,4472136. Làm tròn ba chữ số thập phân là 0,447.</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1111,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
@@ -1121,7 +1129,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bình phương từng chênh lệch trước khi cộng.</t>
+          <t>Khoảng cách Euclidean giữa a = [1, 2, 3] và b = [4, 2, -1]: d(a, b) = √((4 - 1)² + (2 - 2)² + (-1 - 3)²) = √(3² + 0² + (-4)²) = √(9 + 0 + 16) = √25 = 5.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1224,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cùng số chiều chưa chắc cùng không gian đã học.</t>
+          <t>Khi chuyển đổi hoặc thay đổi mô hình embeddings hay metric truy vấn, hai mô hình khác nhau có không gian vector hoàn toàn khác nhau (ngay cả khi cùng số chiều). Do đó, bắt buộc phải xác nhận metric, phương pháp chuẩn hóa và mô hình trên cả kho tài liệu lẫn truy vấn; nếu đổi mô hình phải re-embed toàn bộ kho và lập lại chỉ mục.</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1304,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Vector giống chiều không có nghĩa cùng hệ tọa độ.</t>
+          <t>Khi thay đổi mô hình embeddings cho một kho tài liệu đã chỉ mục, không thể tìm kiếm truy vấn của mô hình mới trên vector cũ vì khác không gian biểu diễn. Bắt buộc phải re-embed toàn bộ kho tài liệu và xây dựng chỉ mục tương thích trước khi chuyển đổi phục vụ.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_02_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_02_22_Cau.xlsx
@@ -624,10 +624,24 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hai lỗi cần hai kiểm soát: phạm vi và mục quá lớn.
-Phân tích theo nguyên lý thiết kế: Hai lỗi cần hai kiểm soát: phạm vi và mục quá lớn.</t>
+- [Chiến lược kết hợp có cấu trúc] (1.5 điểm): Đề xuất phân đoạn theo heading kết hợp chia nhỏ đệ quy khi vượt budget, kèm kế thừa metadata tổ tiên.
+- [Giải pháp neo giữ ngoại lệ] (1.0 điểm): Nêu cơ chế neo giữ ngoại lệ cùng phạm vi với điều kiện chính sách, không để ngắt giữa chừng.
+- [Bằng chứng quyết định thực nghiệm] (1.5 điểm): Xác định rõ 2 chỉ số đo lường trên bộ kiểm thử đóng băng (độ phủ đồng thời điều kiện-ngoại lệ và tỷ lệ nhiễm chéo) cùng ngưỡng nghiệm thu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đề xuất chiến lược kết hợp (Hybrid / Hierarchical Chunking Strategy):
+- Cấu trúc phân đoạn theo tiêu đề kèm phân đoạn con (Heading-aware Section Chunking with Sub-chunking / Parent-Document Retrieval):
+  + Cấp độ 1 (Section Boundary): Phân chia tài liệu theo cấu trúc phân cấp tiêu đề (`#`, `##`, `###`). Mỗi mục chính sách tạo thành một Parent Document tự chứa trọn vẹn ngữ cảnh điều kiện và ngoại lệ.
+  + Cấp độ 2 (Size Budget Enforcement): Nếu một section quá dài (vượt quá ngân sách token tối ưu, ví dụ &gt; 500 tokens), áp dụng Recursive Character Splitting để chia nhỏ thành các Child Chunks, nhưng bắt buộc gắn metadata `parent_id` và sao chép tiêu đề tổ tiên (`breadcrumbs`) vào từng child chunk.
+  + Gắn kết ngoại lệ: Các ghi chú ngoại lệ luôn được neo giữ (anchor) vào cùng block với điều kiện áp dụng tương ứng, không bị ngắt quãng giữa hai chunk.
+2. Bằng chứng quyết định dựa trên bộ kiểm thử đã đóng băng (Empirical Decision Evidence):
+- Đo lường trên bộ câu hỏi đóng băng: Đánh giá bằng 2 chỉ số cụ thể:
+  (a) Tỷ lệ câu hỏi ngoại lệ tìm thấy cả điều kiện lẫn ngoại lệ trong Top-K (Condition &amp; Exception Co-occurrence Recall@5);
+  (b) Tỷ lệ chunk bị nhiễm chéo thông tin giữa hai chính sách khác nhau (Cross-policy Contamination Rate).
+- Điều kiện nghiệm thu chiến lược kết hợp: Đạt Co-occurrence Recall &gt;= 95% (khắc phục lỗi của fixed-window) và Cross-policy Contamination = 0% (khắc phục lỗi của long-heading chunking).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Cửa sổ cố định (fixed window) thường cắt ngang giữa điều kiện và ngoại lệ vì không hiểu ranh giới ngữ nghĩa. Ngược lại, chunking thuần túy theo tiêu đề dễ tạo ra những đoạn quá dài hoặc gộp lẫn nội dung nếu tài liệu viết lỏng lẻo. Giải pháp tối ưu là phân đoạn có cấu trúc phân cấp (Hierarchical/Parent-Child Chunking) kết hợp gắn metadata tổ tiên, được kiểm chứng bằng bộ benchmark cố định với các chỉ số đo lường lỗi cụ thể.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LlamaIndex Documentation: 'Hierarchical Node Parser &amp; Parent Document Retrieval' (https://docs.llamaindex.ai/en/stable/examples/retrievers/auto_merging_retriever/)</t>
         </is>
       </c>
     </row>
@@ -753,10 +767,21 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mức nhỏ nhất đã giữ đủ mối liên hệ là ứng viên mạnh.
-Phân tích theo nguyên lý thiết kế: Mức nhỏ nhất đã giữ đủ mối liên hệ là ứng viên mạnh.</t>
+- [Quyết định chính sách chính xác] (1.5 điểm): Chọn mức overlap nhỏ nhất giữ đủ liên kết (40 ký tự) và bác bỏ có lý lẽ mức 0 (mất liên kết) và mức 180 (trùng lặp, lãng phí top-k).
+- [Phân tích đánh đổi kỹ thuật] (1.5 điểm): Phân tích trade-off rõ ràng giữa bảo toàn ngữ nghĩa liên đoạn và sự đa dạng của tập kết quả truy xuất.
+- [Phương pháp kiểm tra thực nghiệm] (1.0 điểm): Đề xuất cách kiểm tra truy xuất mệnh đề biên và đo lường tỷ lệ trùng lặp nội dung giữa các chunk.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn chính sách Overlap (Overlap Policy Selection):
+Chọn mức overlap nhỏ nhất đủ để bảo toàn liên kết ngữ nghĩa giữa hai chunk kề nhau, trong trường hợp này là `overlap = 40 ký tự` (hoặc mức tương đương 1-2 câu trọn vẹn ngữ nghĩa).
+- Giải thích vì sao không chọn 0: Overlap = 0 tạo ra ranh giới cứng (hard cutoff), làm đứt gãy mối liên hệ giữa điều kiện ở cuối chunk A và ngoại lệ ở đầu chunk B, khiến retriever bỏ sót thông tin liên quan khi câu hỏi yêu cầu cả hai.
+- Giải thích vì sao không chọn 180: Overlap = 180 ký tự quá lớn, chiếm tỷ lệ cao trong chunk, dẫn đến hiện tượng trùng lặp thông tin nghiêm trọng (near-duplicate chunks). Điều này làm cho danh sách Top-K bị chiếm dụng bởi 3 chunk gần giống nhau, làm giảm đa dạng ngữ cảnh (diversity), lãng phí token ngân sách và tăng chi phí LLM.
+2. Phương pháp kiểm thử và xác thực chính sách (Verification Method):
+- Kiểm thử truy xuất (Retrieval Test): Chạy bộ kiểm thử với các query liên đới biên (boundary-spanning queries) và kiểm tra xem cả hai mệnh đề (điều kiện và ngoại lệ) có xuất hiện trong cùng một chunk hoặc trong Top-2 chunk liền kề hay không.
+- Kiểm tra độ dư thừa ngữ cảnh (Redundancy / Deduplication Test): Tính toán điểm tương đồng Jaccard hoặc Cosine giữa các chunk liên tiếp; đảm bảo mức overlap không tạo ra các chunk có độ trùng lặp nội dung &gt; 40%.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc thiết lập chunk overlap tuân theo định lý biên ngữ nghĩa: overlap phải đủ lớn để một ý nghĩa bị cắt ngang ở cuối chunk trước xuất hiện trọn vẹn ở đầu chunk sau, nhưng phải là mức tối thiểu cần thiết để không gây ô nhiễm danh sách Top-K bằng các bản sao gần trùng lặp (redundant chunks), gây nghẽn context window của mô hình tạo sinh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pinecone Learning Center: 'Chunking Strategies for LLM Applications' (https://www.pinecone.io/learn/chunking-strategies/)</t>
         </is>
       </c>
     </row>
@@ -882,10 +907,22 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một vector không biết chính sách nào đang có hiệu lực.
-Phân tích theo nguyên lý thiết kế: Một vector không biết chính sách nào đang có hiệu lực.</t>
+- [Phân tích vai trò của Embedding] (1.5 điểm): Nêu rõ embedding chỉ phản ánh sự tương đồng ngữ nghĩa/chủ đề trong không gian vector biểu diễn.
+- [Chỉ rõ giới hạn bản chất] (1.5 điểm): Khẳng định dứt khoát embedding không đo lường được tính đúng sai, tính cập nhật thời gian hay hiệu lực pháp lý của chính sách.
+- [Đề xuất giải pháp kiến trúc] (1.0 điểm): Đưa ra giải pháp dùng Metadata Filtering quản lý phiên bản và ngày hiệu lực để lọc trước khi truy xuất.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Những điều Embedding vector hỗ trợ kết luận:
+- Hỗ trợ kết luận về độ tương đồng ngữ nghĩa bề mặt và chủ đề (Semantic Topical Similarity): Vector embeddings chuyển đổi văn bản thành tọa độ trong không gian ngữ nghĩa tiềm ẩn. Điểm cosine 0,91 cao hơn 0,87 chứng minh rằng chunk 0,91 có sự tương đồng từ vựng/ngữ nghĩa gần gũi hơn với các từ khóa và ý đồ trong câu hỏi của người dùng so với chunk 0,87.
+2. Những điều Embedding vector KHÔNG hỗ trợ kết luận:
+- Không thể kết luận về tính chân thực khách quan (Factual Truth / Validity): Mô hình embedding không có cơ chế xác minh tính đúng đắn của thông tin.
+- Không thể kết luận về tính cập nhật và hiệu lực pháp lý (Temporal Freshness / Policy Lifecycle): Vector không gian hoàn toàn không có trục thời gian nội tại; nó không biết chính sách nào là bản cũ và chính sách nào là bản hiện hành đang có hiệu lực thi hành.
+- Không thể thay thế bộ lọc trạng thái nghiệp vụ: Một chính sách cũ đã bị thu hồi nhưng viết hay hơn, trùng từ khóa nhiều hơn vẫn có thể có điểm cosine cao hơn chính sách mới.
+3. Giải pháp thiết kế hệ thống bắt buộc:
+Phải tách rời việc tìm kiếm ngữ nghĩa khỏi quản lý vòng đời tài liệu: Sử dụng Metadata Filtering (ví dụ: `is_active: true`, `version: 'v3'`, `effective_date &lt;= CURRENT_DATE`) để sàng lọc trước khi thực hiện tính điểm tương đồng vector.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Không gian embedding phản ánh sự tương đồng hình thức và khái niệm ngữ nghĩa, hoàn toàn bất khả tri (agnostic) đối với tính chân lý và hiệu lực thời gian. Một sai lầm phổ biến trong thiết kế RAG là đồng nhất điểm cosine cao với 'câu trả lời đúng'. Để hệ sinh thái RAG tin cậy, việc kiểm soát phiên bản và hiệu lực bắt buộc phải được giải quyết ở tầng metadata và dữ liệu có cấu trúc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Reimers &amp; Gurevych (2019): 'Sentence-BERT: Sentence Embeddings using Siamese BERT-Networks' (EMNLP 2019) &amp; OpenAI Embeddings Guide</t>
         </is>
       </c>
     </row>
@@ -1093,10 +1130,22 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ phân biệt điểm quan sát được và nguyên nhân mới là giả thuyết.
-Phân tích theo nguyên lý thiết kế: Giữ phân biệt điểm quan sát được và nguyên nhân mới là giả thuyết.</t>
+- [Bản chất điểm quan sát] (1.0 điểm): Nêu đúng điểm cosine chỉ phản ánh góc vector trong không gian tiềm ẩn, không phản ánh độ chi tiết hữu ích.
+- [Điều chưa chứng minh] (1.0 điểm): Phân biệt rõ điểm số cao không chứng minh tính đầy đủ hay câu trả lời đúng trọng tâm nhu cầu người dùng.
+- [Thiết kế thử nghiệm tiếp theo] (1.0 điểm): Đề xuất thử nghiệm cụ thể với Cross-Encoder Reranker hoặc đo lường chất lượng câu trả lời đầu ra.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Điều điểm số Cosine cho biết (Observed Fact):
+Chunk A đạt cosine 0,84 và Chunk B đạt 0,80 cho thấy: theo không gian vector của mô hình embedder hiện tại, vector biểu diễn của Chunk A có góc lệch nhỏ hơn so với vector truy vấn so với Chunk B. Điều này chỉ phản ánh mức độ trùng khớp ngữ nghĩa bề mặt (surface semantic overlap) hoặc chứa nhiều từ vựng bao quát chủ đề của câu hỏi.
+2. Điều điểm số CHƯA chứng minh (Unproven Hypotheses):
+- Chưa chứng minh Chunk A là câu trả lời tốt hơn cho người dùng. Thực tế Chunk A chỉ nói chung chung trong khi Chunk B mới chứa câu trả lời cụ thể có thể hành động được.
+- Chưa chứng minh mô hình embedder hiểu được chiều sâu nghiệp vụ; các embedder dạng bi-encoder thường bị thiên vị (bias) đối với các đoạn văn bản chứa nhiều từ khóa tần suất cao hoặc các câu khẳng định chung.
+3. Thử nghiệm kế tiếp (Next Controlled Experiment):
+- Thử nghiệm 1 (Tầng Re-ranking): Đưa cả Top-K (bao gồm Chunk A và B) qua một mô hình Cross-Encoder Re-ranker (ví dụ: BGE-Reranker-Large hoặc Cohere Rerank) để đánh giá độ liên quan thực sự ở cấp độ tương tác qua lại giữa query và document.
+- Thử nghiệm 2 (End-to-End Generation &amp; Human/LLM Evaluation): Đưa lần lượt Chunk A và Chunk B vào context của generator và đo lường Answer Relevance / Completeness trên bộ câu hỏi thử nghiệm chuẩn hóa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Điểm số Cosine từ Bi-Encoder chỉ là phép ước lượng gần đúng về sự gần gũi trong không gian tiềm ẩn (latent space), thường ưu tiên các văn bản tổng quát có mật độ từ khóa cao. Điểm số quan sát được không đồng nghĩa với giá trị thông tin thực tế. Quy trình hai tầng (Two-stage Retrieval: Bi-encoder retrieval + Cross-encoder reranking) là giải pháp tiêu chuẩn để giải quyết sự sai lệch này.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Thakur et al. (2021): 'BEIR: A Heterogeneous Benchmark for Zero-shot Evaluation of Information Retrieval Models' (NeurIPS 2021)</t>
         </is>
       </c>
     </row>
@@ -1255,10 +1304,24 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một mô hình không đáp ứng độ trễ SLO không phải lựa chọn mặc định.
-Phân tích theo nguyên lý thiết kế: Một mô hình không đáp ứng độ trễ SLO không phải lựa chọn mặc định.</t>
+- [Quyết định chọn Model A có căn cứ] (1.5 điểm): Chọn Mô hình A vì thỏa mãn SLO p95 &lt;= 100ms, loại Mô hình B vì vi phạm SLO (190ms) và chi phí RAM 3072d cho 5M chunk quá cao.
+- [Nhận diện hạn chế của Model A] (1.0 điểm): Nêu rõ hạn chế về Recall@5 thấp hơn 2% trên tập ngữ liệu Việt–Anh.
+- [Điều kiện xem xét lại lựa chọn] (1.5 điểm): Đưa ra các điều kiện cụ thể: kỹ thuật lượng tử hóa (quantization/Matryoshka), tối ưu hạ tầng đạt SLO latency, và ngân sách re-indexing 5M chunk.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn mô hình cho đợt phát hành hiện tại:
+Chọn **Mô hình A** (768 chiều, Recall@5 = 0,86, p95 latency = 45 ms).
+Căn cứ quyết định: Tiêu chí SLO kỹ thuật quy định nghiêm ngặt độ trễ `p95 &lt;= 100 ms`. Mô hình B có Recall@5 nhỉnh hơn 2% (0,88 vs 0,86) nhưng độ trễ p95 lên tới 190 ms, vi phạm nghiêm trọng SLO kỹ thuật (vượt 90% giới hạn cho phép). Ngoài ra, Mô hình B có 3.072 chiều (gấp 4 lần Mô hình A), sẽ làm tăng gấp 4 lần dung lượng RAM lưu trữ index cho 5 triệu chunk, đẩy chi phí hạ tầng và độ trễ tìm kiếm vector lên rất cao mà không mang lại lợi ích tương xứng.
+2. Các hạn chế của Mô hình A:
+- Độ bao phủ Recall@5 thấp hơn Mô hình B 2% trên bộ kiểm thử Việt–Anh, có nguy cơ bỏ sót một số tài liệu hiếm hoặc câu hỏi đa ngữ phức tạp.
+- Khả năng biểu diễn ngữ nghĩa đa chiều trong các lĩnh vực chuyên sâu có thể kém hơn các mô hình embedding kích thước lớn (large dimensional embeddings).
+3. Điều kiện để xem xét lại lựa chọn (Re-evaluation Criteria):
+- Khi áp dụng các kỹ thuật tối ưu hóa chỉ mục cho Mô hình B thành công: như lượng tử hóa vector (Scalar Quantization SQ8 hoặc Product Quantization PQ) hoặc Matryoshka Embeddings cắt ngắn chiều xuống 768/1536 mà vẫn giữ recall cao và hạ p95 xuống dưới 80 ms.
+- Khi nâng cấp hạ tầng phần cứng (GPU indexing / HNSW acceleration) giúp hạ p95 của Mô hình B vào phạm vi SLO hợp lệ.
+- Khi có ngân sách tài chính và thời gian bảo trì được duyệt để chi trả chi phí re-embed cho toàn bộ 5 triệu chunk tài liệu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kỹ thuật hệ thống sản xuất (Production Engineering), việc tuân thủ SLO (Service Level Objective) là điều kiện tiên quyết bắt buộc (hard constraint). Một mô hình dù có độ chính xác cao hơn nhưng vi phạm SLO độ trễ sẽ bị loại bỏ khỏi danh sách triển khai thực tế. Việc chuyển đổi mô hình embedding trên tập dữ liệu lớn (5M chunks) phải tính toán toàn diện giữa chi phí tính toán lại, dung lượng RAM chỉ mục và độ trễ phục vụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: 'Service Level Objectives and Latency Budgets' &amp; Pinecone Benchmark: 'Embedding Dimension vs Latency and Memory Footprint'</t>
         </is>
       </c>
     </row>
@@ -1531,10 +1594,22 @@
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: top-k không tạo thêm bản ghi.
-Phân tích theo nguyên lý thiết kế: top-k không tạo thêm bản ghi.</t>
+- [Kết quả của Kho A] (1.5 điểm): Xác định đúng Kho A trả về chính xác 2 bản ghi (áp dụng min(N, k)), không tạo bản ghi ảo.
+- [Kết quả của Kho B] (1.0 điểm): Xác định đúng Kho B trả về danh sách rỗng [] an toàn, không báo lỗi sập hệ thống.
+- [Quy tắc sắp xếp khi bằng điểm] (1.5 điểm): Nêu rõ cơ chế tie-breaking theo record_id tăng dần để đảm bảo tính tất định và khả năng tái lập.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kết quả mong đợi cho mỗi kho dữ liệu:
+- Với Kho A (đang có 2 bản ghi, yêu cầu `top_k = 5`):
+  + Kết quả trả về: Trả về chính xác **2 bản ghi**. Thuật toán Top-K truy xuất tối đa `k` ứng viên hiện có trong kho; nếu số lượng bản ghi thỏa mãn điều kiện nhỏ hơn `k`, hệ thống chỉ trả về toàn bộ các bản ghi tìm thấy (`min(N, k)`), tuyệt đối không tự bịa thêm bản ghi giả lập hay trả về các phần tử rác.
+- Với Kho B (kho rỗng, yêu cầu `top_k = 5`):
+  + Kết quả trả về: Trả về danh sách rỗng `[]` (empty list) với mã trạng thái thành công (HTTP 200 OK), không sinh lỗi ngoại lệ hệ thống.
+2. Quy tắc sắp xếp khi điểm số tương đồng bằng nhau (Tie-breaking Rule):
+- Quy tắc: Khi hai hoặc nhiều bản ghi có điểm tương đồng cosine/similarity bằng nhau (ví dụ cùng bằng 0.8500), hệ thống áp dụng cơ chế xác định thứ tự đơn định (Deterministic Tie-breaking) bằng cách so sánh trường `record_id` theo thứ tự tăng dần (ascending order: `record_id_1 &lt; record_id_2`).
+- Tầm quan trọng: Đảm bảo tính nhất quán và khả năng tái lập (idempotency/reproducibility) của kết quả tìm kiếm qua các lần gọi API khác nhau.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Giao diện tìm kiếm vector ngữ nghĩa (Vector Semantic Search) phải tuân thủ chặt chẽ hợp đồng API: trả về `min(count_matching, k)` phần tử. Khi có hiện tượng bằng điểm (tie), nếu không quy định thứ tự tie-breaking bằng một khóa đơn định duy nhất (như record_id), thứ tự trả về sẽ phụ thuộc vào cách duyệt vùng nhớ của thuật toán tìm kiếm gần đúng (ANN), gây ra lỗi không nhất quán dữ liệu giữa các lần truy vấn giống hệt nhau.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Milvus Documentation: 'Vector Search Query Parameters, Limit/Top-K and Consistency' (https://milvus.io/docs/search.md)</t>
         </is>
       </c>
     </row>
